--- a/Docx & xslx/PySpark_functions.xlsx
+++ b/Docx & xslx/PySpark_functions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CSE-A\Learning Pyspark\Docx &amp; xslx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4928B415-9DA9-4C63-9AF0-AA05B1F25F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA126C9C-59C8-44DE-8B08-D1D7F82D259C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{75F2D982-5AAE-DD43-9C6D-7C4DEB1D1754}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="422">
   <si>
     <t># PYSPARK IMPORTANT FUNCTIONS LIST</t>
   </si>
@@ -1401,6 +1401,9 @@
       </rPr>
       <t xml:space="preserve"> May 2026 (Complted upto this line)</t>
     </r>
+  </si>
+  <si>
+    <t>04 June 2026 completed upto this</t>
   </si>
 </sst>
 </file>
@@ -3699,6 +3702,11 @@
         <v>215</v>
       </c>
     </row>
+    <row r="581" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A581" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
     <row r="582" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>216</v>
